--- a/ORANGEHRM.xlsx
+++ b/ORANGEHRM.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2831E4D2-888E-4AB9-ABF9-6A579B04B40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BAD8AC-42A8-4BF0-B4E8-87A5236881BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB7E9C57-DAB0-4D4D-B453-7A4042C8BB09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{DB7E9C57-DAB0-4D4D-B453-7A4042C8BB09}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Test Scenario" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
+    <sheet name="Bug Reports" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,17 +30,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="125">
   <si>
     <t>SND</t>
   </si>
   <si>
-    <t>Req#ID</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
     <t>3.1.1</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
   </si>
   <si>
     <t>Verify login with valid ESS username and valid password</t>
-  </si>
-  <si>
-    <t>Steps</t>
   </si>
   <si>
     <t>1) Launch browser
@@ -99,40 +90,7 @@
 5)Click on Login button</t>
   </si>
   <si>
-    <t>TC#ID</t>
-  </si>
-  <si>
-    <t>Project/Module Name</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_001</t>
-  </si>
-  <si>
     <t>Orange HRM-Myinfo</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_002</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_003</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_004</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_005</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_006</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_007</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_008</t>
-  </si>
-  <si>
-    <t>TC_Myinfo_009</t>
   </si>
   <si>
     <t>Verify login with valid ESS username and invalid password</t>
@@ -168,36 +126,13 @@
     <t>Test Data</t>
   </si>
   <si>
-    <t>pavan11/pavan@123</t>
-  </si>
-  <si>
-    <t>pavan11/abc123</t>
-  </si>
-  <si>
-    <t>sita22/pavan@123</t>
-  </si>
-  <si>
-    <t>hari45/hello0923</t>
-  </si>
-  <si>
     <t>Expected Results</t>
   </si>
   <si>
-    <t>Login successful.
-ESS user should see Myinfo page after login successful.</t>
-  </si>
-  <si>
     <t>Invalid credentials</t>
   </si>
   <si>
     <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Dashboard is displayed after login is 
-successful instead of Myinfo page.</t>
-  </si>
-  <si>
-    <t>As expected</t>
   </si>
   <si>
     <t>Status(Passed/Fail)</t>
@@ -248,16 +183,6 @@
 3)Click on Contact Details link</t>
   </si>
   <si>
-    <t>ESS user can edit personal details</t>
-  </si>
-  <si>
-    <t>ESS user cannot edit restricted fields in
-Personal details</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to view Contact Details</t>
-  </si>
-  <si>
     <t>Verify ESS user can edit personal details</t>
   </si>
   <si>
@@ -265,9 +190,6 @@
   </si>
   <si>
     <t>Verify ESS user can add a photograph</t>
-  </si>
-  <si>
-    <t>ESS user is able to view Contact Details</t>
   </si>
   <si>
     <t>NA</t>
@@ -292,24 +214,6 @@
 file format(.exe)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">As expected
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Clarification Required on SSN NO.
-(Not visible on Myinfo-&gt;Personal 
-details page)</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">The message of "Invalid file type" should
 appear (as only JPG,GIF and PNG files supported)
 after the Upload buttom.But it uploads the 
@@ -320,9 +224,6 @@
     <t>Partially Passed</t>
   </si>
   <si>
-    <t>Failed(P2)</t>
-  </si>
-  <si>
     <t>User should be able to view Contact details</t>
   </si>
   <si>
@@ -330,30 +231,15 @@
 </t>
   </si>
   <si>
-    <t>QA</t>
-  </si>
-  <si>
     <t>Bug ID</t>
   </si>
   <si>
-    <t>Module Name</t>
-  </si>
-  <si>
-    <t>Build No</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>TCID</t>
-  </si>
-  <si>
     <t>Steps to replicate bug</t>
   </si>
   <si>
-    <t>Screenshot</t>
-  </si>
-  <si>
     <t>Severity</t>
   </si>
   <si>
@@ -366,9 +252,6 @@
     <t>Assigned To</t>
   </si>
   <si>
-    <t>Resolution</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -381,13 +264,6 @@
     <t>ORHRM_002</t>
   </si>
   <si>
-    <t>Dashboard is displayed after login is successful instead of Nyinfo page</t>
-  </si>
-  <si>
-    <t>The invalid file format error message for invalid photograph is 
-appearing after the upload is complete.</t>
-  </si>
-  <si>
     <t>S3</t>
   </si>
   <si>
@@ -400,14 +276,7 @@
     <t>John</t>
   </si>
   <si>
-    <t>Accepted</t>
-  </si>
-  <si>
     <t>InProgress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
   </si>
   <si>
     <t xml:space="preserve">1)Login to OrangeHRM as ESS user
@@ -426,6 +295,193 @@
 3)provide valid ESS user name
 4)provide valid password
 5)Click on Login button.</t>
+  </si>
+  <si>
+    <t>TC ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Req ID</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>ESS User Login</t>
+  </si>
+  <si>
+    <t>Emergency Contacts</t>
+  </si>
+  <si>
+    <t>Login successful; user is redirected directly to the My Info page.</t>
+  </si>
+  <si>
+    <t>Redirection goes to Dashboard page instead of My Info.</t>
+  </si>
+  <si>
+    <t>Username: Admin
+password : admin123</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_001</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_002</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_003</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_004</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_005</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_006</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_007</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_008</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_009</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_010</t>
+  </si>
+  <si>
+    <t>Username: Admin
+password : abcder546</t>
+  </si>
+  <si>
+    <t>Invalid credentials message displayed as expected.</t>
+  </si>
+  <si>
+    <t>Username:admin12
+Password:admin123</t>
+  </si>
+  <si>
+    <t>Username:admin12
+Password:hello</t>
+  </si>
+  <si>
+    <t>ESS user Login - Invalid Password</t>
+  </si>
+  <si>
+    <t>ESS user Login - Invalid Username</t>
+  </si>
+  <si>
+    <t>ESS user Login - Both Invalid</t>
+  </si>
+  <si>
+    <t>Verify Restricted Fields in Personal Details</t>
+  </si>
+  <si>
+    <t>Edit Personal Details</t>
+  </si>
+  <si>
+    <t>Add/Upload Profile Photograph</t>
+  </si>
+  <si>
+    <t>View Contact Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1)Login to OrangeHRM as ESS user
+2)Click on Myinfo tab
+3)Click on Emergency Contacts </t>
+  </si>
+  <si>
+    <t>User should be able to view Emergency Contact details.</t>
+  </si>
+  <si>
+    <t>User can view Personal Details as expected.</t>
+  </si>
+  <si>
+    <t>User is able to edit and save details as expected.</t>
+  </si>
+  <si>
+    <t>Contact details visible as expected.</t>
+  </si>
+  <si>
+    <t>Emergency Contacts visible as expected.</t>
+  </si>
+  <si>
+    <t>Related TC</t>
+  </si>
+  <si>
+    <t>Successful ESS login redirects user to Dashboard instead
+ of the expected My Info landing page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The invalid file format error message for invalid photograph
+ is displayed after the upload is complete.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. OrangeHRM application is accessible.
+2. A valid ESS user account exists.
+</t>
+  </si>
+  <si>
+    <t>1. OrangeHRM application is accessible.
+2. A valid ESS user account exists.</t>
+  </si>
+  <si>
+    <t>1. OrangeHRM application is accessible. 
+2. A valid ESS user account exists.</t>
+  </si>
+  <si>
+    <t>1. OrangeHRM application is accessible.</t>
+  </si>
+  <si>
+    <t>1. User is authenticated and logged in as an ESS user.</t>
+  </si>
+  <si>
+    <t>1. User is logged in as an ESS user.
+2. User is on the My Info &gt; Personal Details page.
+3. Edit permissions are enabled for editable fields</t>
+  </si>
+  <si>
+    <t>1. User is logged in as an ESS user.
+2. User is on the My Info &gt; Personal Details page.</t>
+  </si>
+  <si>
+    <t>1. User is logged in as an ESS user.
+2. User is on the My Info profile page.
+3. Unsupported file type (e.g., .pdf or .txt) is available locally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. User is authenticated and logged in as an ESS user.
+</t>
+  </si>
+  <si>
+    <t>1. User is authenticated and logged in as an ESS user</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to view Contact Details page.</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to view Emergency Contact page.</t>
+  </si>
+  <si>
+    <t>REQ ID</t>
+  </si>
+  <si>
+    <t>Scenarios</t>
+  </si>
+  <si>
+    <t>Employee ID, SIN No., Driver License No., and Date of Birth are non-editable as expected. However, the SSN No. field is not visible on the Personal Details page; therefore, its edit restriction could not be verified.</t>
   </si>
 </sst>
 </file>
@@ -547,7 +603,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -592,6 +648,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -617,13 +679,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>342599</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>207754</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>2228150</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>966248</xdr:rowOff>
@@ -651,55 +713,6 @@
         <a:xfrm>
           <a:off x="13712950" y="7537094"/>
           <a:ext cx="1885551" cy="758494"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>105058</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>10026</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3980448</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>2175711</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E98908E6-5A0E-420E-A720-37D7125D3074}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9289163" y="370973"/>
-          <a:ext cx="3875390" cy="2165685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1019,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1030,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1041,10 +1054,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1052,10 +1065,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1063,10 +1076,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1074,10 +1087,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1085,10 +1098,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1096,10 +1109,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1107,10 +1120,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1118,10 +1131,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1129,10 +1142,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1162,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3112369-3159-4036-8204-3F9129DFDE1A}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -1170,370 +1183,426 @@
     <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="53.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="49.77734375" customWidth="1"/>
-    <col min="7" max="7" width="36.77734375" customWidth="1"/>
-    <col min="8" max="8" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.6640625" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="53.5546875" customWidth="1"/>
+    <col min="7" max="7" width="49.77734375" customWidth="1"/>
+    <col min="8" max="8" width="36.77734375" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="55.6640625" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="H2" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F4" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="F7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J7" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="K9" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="C10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G12" s="1"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="6"/>
+      <c r="G13" s="1"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1544,189 +1613,149 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G15" s="4"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G16" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G17" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="I12:K12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{48C8E00A-9F4B-40B0-9F85-DEB7E786349F}"/>
-    <hyperlink ref="G4" r:id="rId2" xr:uid="{34D6AA7B-5FA3-4BC8-A57D-0C1658B3210E}"/>
+    <hyperlink ref="H2" r:id="rId1" display="pavan11/pavan@123" xr:uid="{48C8E00A-9F4B-40B0-9F85-DEB7E786349F}"/>
+    <hyperlink ref="H4" r:id="rId2" display="sita22/pavan@123" xr:uid="{34D6AA7B-5FA3-4BC8-A57D-0C1658B3210E}"/>
+    <hyperlink ref="I3" r:id="rId3" display="pavan11/pavan@123+I2:J+I3" xr:uid="{A542F68F-1295-4329-A2F1-1960635F723A}"/>
+    <hyperlink ref="H5" r:id="rId4" display="sita22/pavan@123" xr:uid="{03484AC4-AFD9-4BE6-8EBC-42C8FC18333B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2953612A-1F27-4CD9-BC05-2004DE67FABE}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A3:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.77734375" customWidth="1"/>
-    <col min="7" max="7" width="60.88671875" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="C4" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="J2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M2" t="s">
-        <v>91</v>
-      </c>
-      <c r="N2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="18">
-        <v>1</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="18">
-        <v>1</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>101</v>
+      <c r="C5" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>